--- a/РАБОЧИЙ СТОЛ/расчет ПОКОМ КИ/машины ПОКОМ КИ.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчет ПОКОМ КИ/машины ПОКОМ КИ.xlsx
@@ -1,31 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчет ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59EA6483-04D5-4B15-8767-EF86BBAD3EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4EA04A-8756-44E7-AF2D-054917C7A679}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
   <si>
     <t>Бердянск</t>
   </si>
@@ -45,9 +51,6 @@
     <t>ПОЛУЧАТЕЛЬ</t>
   </si>
   <si>
-    <t>3 машина</t>
-  </si>
-  <si>
     <t>Остаток</t>
   </si>
   <si>
@@ -75,9 +78,6 @@
     <t>Бейдерман</t>
   </si>
   <si>
-    <t>4 машина</t>
-  </si>
-  <si>
     <t>Малахутин</t>
   </si>
   <si>
@@ -108,12 +108,6 @@
     <t>Обрыньба</t>
   </si>
   <si>
-    <t>1 машина на 27,06</t>
-  </si>
-  <si>
-    <t>1 машина на 26,06</t>
-  </si>
-  <si>
     <t>Логистон (ПРС)</t>
   </si>
   <si>
@@ -121,6 +115,21 @@
   </si>
   <si>
     <t>Кочевой НВ</t>
+  </si>
+  <si>
+    <t>1 машина на 04,07</t>
+  </si>
+  <si>
+    <t>мало</t>
+  </si>
+  <si>
+    <t>2 машина на 04,07</t>
+  </si>
+  <si>
+    <t>1 машина на 05,07</t>
+  </si>
+  <si>
+    <t>2 машина на 05,07</t>
   </si>
 </sst>
 </file>
@@ -151,7 +160,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -167,6 +176,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -621,12 +636,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -651,8 +668,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -933,7 +948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
@@ -951,95 +966,99 @@
     <col min="17" max="17" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="32"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="32"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="28" t="s">
+      <c r="F1" s="34"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="34"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="34"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="34"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="32"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="32"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+    </row>
+    <row r="2" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="31"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
       <c r="E2" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="G2" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="19" t="s">
-        <v>13</v>
-      </c>
       <c r="H2" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="J2" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="19" t="s">
-        <v>13</v>
-      </c>
       <c r="K2" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="M2" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="19" t="s">
-        <v>13</v>
-      </c>
       <c r="N2" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="P2" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q2" s="27"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q2" s="29"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="26">
         <v>1534</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
+      <c r="C3" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>29</v>
+      </c>
       <c r="E3" s="6"/>
       <c r="F3" s="3"/>
       <c r="G3" s="7"/>
@@ -1057,16 +1076,18 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="35" t="s">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22">
-        <v>30800</v>
-      </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="4"/>
+      <c r="B4" s="20">
+        <v>24394</v>
+      </c>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="4">
+        <v>17485</v>
+      </c>
       <c r="F4" s="2"/>
       <c r="G4" s="5"/>
       <c r="H4" s="4"/>
@@ -1075,27 +1096,42 @@
       <c r="K4" s="4"/>
       <c r="L4" s="2"/>
       <c r="M4" s="5"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="5"/>
+      <c r="N4" s="4">
+        <v>6909</v>
+      </c>
+      <c r="O4" s="2">
+        <v>7662</v>
+      </c>
+      <c r="P4" s="5">
+        <v>12</v>
+      </c>
       <c r="Q4" s="8">
         <f t="shared" ref="Q4:Q21" si="0">B4-E4-H4-K4-N4</f>
-        <v>30800</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>-6400</v>
+      </c>
+      <c r="S4">
+        <f>B4+R4</f>
+        <v>17994</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="22">
-        <v>15644</v>
-      </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
+      <c r="B5" s="20">
+        <v>17262</v>
+      </c>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="4"/>
       <c r="F5" s="2"/>
       <c r="G5" s="5"/>
-      <c r="H5" s="4"/>
+      <c r="H5" s="4">
+        <v>17262</v>
+      </c>
       <c r="I5" s="2"/>
       <c r="J5" s="5"/>
       <c r="K5" s="4"/>
@@ -1106,25 +1142,27 @@
       <c r="P5" s="5"/>
       <c r="Q5" s="8">
         <f t="shared" si="0"/>
-        <v>15644</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="22">
-        <v>11035</v>
-      </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
+      <c r="B6" s="20">
+        <v>17335</v>
+      </c>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="4"/>
       <c r="F6" s="2"/>
       <c r="G6" s="5"/>
       <c r="H6" s="4"/>
       <c r="I6" s="2"/>
       <c r="J6" s="5"/>
-      <c r="K6" s="4"/>
+      <c r="K6" s="4">
+        <v>17335</v>
+      </c>
       <c r="L6" s="2"/>
       <c r="M6" s="5"/>
       <c r="N6" s="4"/>
@@ -1132,16 +1170,16 @@
       <c r="P6" s="5"/>
       <c r="Q6" s="8">
         <f t="shared" si="0"/>
-        <v>11035</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
+        <v>8</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="4"/>
       <c r="F7" s="2"/>
       <c r="G7" s="5"/>
@@ -1159,13 +1197,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
+        <v>14</v>
+      </c>
+      <c r="B8" s="20"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="4"/>
       <c r="F8" s="2"/>
       <c r="G8" s="5"/>
@@ -1183,13 +1221,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="4"/>
       <c r="F9" s="2"/>
       <c r="G9" s="5"/>
@@ -1207,13 +1245,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
+        <v>22</v>
+      </c>
+      <c r="B10" s="22"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="9"/>
       <c r="F10" s="10"/>
       <c r="G10" s="11"/>
@@ -1231,17 +1269,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="24">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="22">
         <v>6209</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="23">
         <v>6881</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="23">
         <v>12</v>
       </c>
       <c r="E11" s="9"/>
@@ -1253,25 +1291,31 @@
       <c r="K11" s="9"/>
       <c r="L11" s="10"/>
       <c r="M11" s="11"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="11"/>
+      <c r="N11" s="9">
+        <v>6209</v>
+      </c>
+      <c r="O11" s="10">
+        <v>6881</v>
+      </c>
+      <c r="P11" s="11">
+        <v>12</v>
+      </c>
       <c r="Q11" s="8">
         <f t="shared" si="0"/>
-        <v>6209</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="22">
         <v>656</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="23">
         <v>742</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="23">
         <v>2</v>
       </c>
       <c r="E12" s="9"/>
@@ -1283,25 +1327,31 @@
       <c r="K12" s="9"/>
       <c r="L12" s="10"/>
       <c r="M12" s="11"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="11"/>
+      <c r="N12" s="9">
+        <v>656</v>
+      </c>
+      <c r="O12" s="10">
+        <v>742</v>
+      </c>
+      <c r="P12" s="11">
+        <v>2</v>
+      </c>
       <c r="Q12" s="8">
         <f t="shared" si="0"/>
-        <v>656</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="22">
         <v>2112</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="23">
         <v>2500</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="23">
         <v>5</v>
       </c>
       <c r="E13" s="9"/>
@@ -1313,21 +1363,27 @@
       <c r="K13" s="9"/>
       <c r="L13" s="10"/>
       <c r="M13" s="11"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="11"/>
+      <c r="N13" s="9">
+        <v>2112</v>
+      </c>
+      <c r="O13" s="10">
+        <v>2500</v>
+      </c>
+      <c r="P13" s="11">
+        <v>5</v>
+      </c>
       <c r="Q13" s="8">
         <f t="shared" si="0"/>
-        <v>2112</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
+        <v>25</v>
+      </c>
+      <c r="B14" s="22"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
       <c r="E14" s="9"/>
       <c r="F14" s="10"/>
       <c r="G14" s="11"/>
@@ -1345,13 +1401,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
+        <v>16</v>
+      </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
       <c r="E15" s="9"/>
       <c r="F15" s="10"/>
       <c r="G15" s="11"/>
@@ -1369,13 +1425,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
+        <v>17</v>
+      </c>
+      <c r="B16" s="22"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
       <c r="E16" s="9"/>
       <c r="F16" s="10"/>
       <c r="G16" s="11"/>
@@ -1395,11 +1451,11 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
+        <v>18</v>
+      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
       <c r="E17" s="4"/>
       <c r="F17" s="2"/>
       <c r="G17" s="5"/>
@@ -1418,16 +1474,16 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="24">
+      <c r="A18" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="22">
         <v>1560</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="23">
         <v>1727</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="23">
         <v>3</v>
       </c>
       <c r="E18" s="9"/>
@@ -1439,21 +1495,27 @@
       <c r="K18" s="9"/>
       <c r="L18" s="10"/>
       <c r="M18" s="11"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="11"/>
+      <c r="N18" s="9">
+        <v>1560</v>
+      </c>
+      <c r="O18" s="10">
+        <v>1727</v>
+      </c>
+      <c r="P18" s="11">
+        <v>3</v>
+      </c>
       <c r="Q18" s="8">
         <f t="shared" ref="Q18:Q20" si="1">B18-E18-H18-K18-N18</f>
-        <v>1560</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
+        <v>15</v>
+      </c>
+      <c r="B19" s="22"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
       <c r="E19" s="9"/>
       <c r="F19" s="10"/>
       <c r="G19" s="11"/>
@@ -1473,11 +1535,11 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="24"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
+        <v>24</v>
+      </c>
+      <c r="B20" s="22"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
       <c r="E20" s="9"/>
       <c r="F20" s="10"/>
       <c r="G20" s="11"/>
@@ -1497,11 +1559,11 @@
     </row>
     <row r="21" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="B21" s="22"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
       <c r="E21" s="4"/>
       <c r="F21" s="10"/>
       <c r="G21" s="11"/>
@@ -1521,14 +1583,14 @@
     </row>
     <row r="22" spans="1:17" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B22" s="13">
         <f t="shared" ref="B22:M22" si="2">SUM(B3:B21)</f>
-        <v>69550</v>
+        <v>71062</v>
       </c>
       <c r="C22" s="13">
-        <f t="shared" si="2"/>
+        <f>SUM(C3:C21)</f>
         <v>11850</v>
       </c>
       <c r="D22" s="13">
@@ -1537,7 +1599,7 @@
       </c>
       <c r="E22" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>17485</v>
       </c>
       <c r="F22" s="14">
         <f t="shared" si="2"/>
@@ -1549,7 +1611,7 @@
       </c>
       <c r="H22" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>17262</v>
       </c>
       <c r="I22" s="14">
         <f t="shared" si="2"/>
@@ -1561,7 +1623,7 @@
       </c>
       <c r="K22" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>17335</v>
       </c>
       <c r="L22" s="14">
         <f t="shared" si="2"/>
@@ -1573,25 +1635,28 @@
       </c>
       <c r="N22" s="12">
         <f t="shared" ref="N22:P22" si="3">SUM(N3:N21)</f>
-        <v>0</v>
+        <v>17446</v>
       </c>
       <c r="O22" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>19512</v>
       </c>
       <c r="P22" s="15">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Q22" s="16">
         <f>SUM(Q3:Q21)</f>
-        <v>69550</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B24">
         <f>B22/17500</f>
-        <v>3.9742857142857142</v>
+        <v>4.0606857142857145</v>
+      </c>
+      <c r="D24">
+        <v>41400</v>
       </c>
     </row>
   </sheetData>
